--- a/data/dictionary/dictionary_v14.0.0.xlsx
+++ b/data/dictionary/dictionary_v14.0.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akdeniz\Documents\python_play_zone\ODS_symposium\data\dictionary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akdeniz\Documents\python_play_zone\ODS_symposium\LIS\v.1.0.2\data\dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E28EFEB-579D-4B89-BB02-2350873F926D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631C79B3-BF9B-451D-B9FB-1973071B9607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="9930" windowWidth="29010" windowHeight="5655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2850" yWindow="2850" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -576,7 +576,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>8.5</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -973,10 +973,10 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0.3</v>
